--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093929F1-8607-9644-A157-E6BA776D3809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CB8B1B-971C-F04A-ADF2-F3B8687BD02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1840" yWindow="1660" windowWidth="17740" windowHeight="14320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1626,24 +1626,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O40" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O40" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:O40" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3597,7 +3597,7 @@
         <v>445</v>
       </c>
       <c r="M40" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>31</v>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CB8B1B-971C-F04A-ADF2-F3B8687BD02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21DB9B7-6722-3A4E-8A56-337DAF510C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="1660" windowWidth="17740" windowHeight="14320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1840" yWindow="1660" windowWidth="17740" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="447">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1501,6 +1501,9 @@
   </si>
   <si>
     <t>#propresenter, #network</t>
+  </si>
+  <si>
+    <t>ZVVU-A001, ZVVU-A002, ZVVU-A003, 2604-2403,2604-2402,2604-2401</t>
   </si>
 </sst>
 </file>
@@ -2159,7 +2162,7 @@
         <v>28</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>29</v>
+        <v>446</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>46</v>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21DB9B7-6722-3A4E-8A56-337DAF510C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A5C5A5-85A3-964E-A992-4100A2A75E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="1660" windowWidth="17740" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="66240" yWindow="-30680" windowWidth="40140" windowHeight="30820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="456">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1504,6 +1504,33 @@
   </si>
   <si>
     <t>ZVVU-A001, ZVVU-A002, ZVVU-A003, 2604-2403,2604-2402,2604-2401</t>
+  </si>
+  <si>
+    <t>Operator Display goes Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When using the ProPresenter computer, cumu-g002, the display goes black for a few seconds. </t>
+  </si>
+  <si>
+    <t>Normal usage of the ProPresenter computer on-site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root cause not yet determined, but likley related to the KVM. </t>
+  </si>
+  <si>
+    <t>No recovery steps known other than count to "3". :(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUMU-G002, 2311-2701, 2603-1105, 2603-1106 </t>
+  </si>
+  <si>
+    <t>#propresenter, #kvm</t>
+  </si>
+  <si>
+    <t>Disucssing isssue with AvAccess Vendor</t>
+  </si>
+  <si>
+    <t>KB0039</t>
   </si>
 </sst>
 </file>
@@ -1629,8 +1656,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O40" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O40" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O41" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O41" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="KB0039"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="13"/>
@@ -1969,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -2025,7 +2058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -2048,7 +2081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -2089,7 +2122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -2133,7 +2166,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
@@ -2174,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
@@ -2218,7 +2251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
@@ -2259,7 +2292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -2300,7 +2333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -2341,7 +2374,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>76</v>
       </c>
@@ -2379,7 +2412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
@@ -2420,7 +2453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>94</v>
       </c>
@@ -2461,7 +2494,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>99</v>
       </c>
@@ -2502,7 +2535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
@@ -2546,7 +2579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>117</v>
       </c>
@@ -2590,7 +2623,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>126</v>
       </c>
@@ -2634,7 +2667,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>135</v>
       </c>
@@ -2675,7 +2708,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>144</v>
       </c>
@@ -2716,7 +2749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -2757,7 +2790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>162</v>
       </c>
@@ -2798,7 +2831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>170</v>
       </c>
@@ -2842,7 +2875,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>180</v>
       </c>
@@ -2886,7 +2919,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>190</v>
       </c>
@@ -2930,7 +2963,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>201</v>
       </c>
@@ -2974,7 +3007,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>211</v>
       </c>
@@ -3012,7 +3045,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>218</v>
       </c>
@@ -3056,7 +3089,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>227</v>
       </c>
@@ -3100,7 +3133,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>239</v>
       </c>
@@ -3144,7 +3177,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>248</v>
       </c>
@@ -3188,7 +3221,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>257</v>
       </c>
@@ -3232,7 +3265,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>266</v>
       </c>
@@ -3276,7 +3309,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>275</v>
       </c>
@@ -3317,7 +3350,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>285</v>
       </c>
@@ -3361,7 +3394,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>292</v>
       </c>
@@ -3405,7 +3438,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>301</v>
       </c>
@@ -3446,7 +3479,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>310</v>
       </c>
@@ -3493,7 +3526,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>320</v>
       </c>
@@ -3537,7 +3570,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>190</v>
       </c>
@@ -3551,7 +3584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>430</v>
       </c>
@@ -3565,7 +3598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>431</v>
       </c>
@@ -3604,6 +3637,50 @@
       </c>
       <c r="N40" s="1" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="M41" s="1">
+        <v>41</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A5C5A5-85A3-964E-A992-4100A2A75E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA142B3B-B051-E946-A335-B94B65C85525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66240" yWindow="-30680" windowWidth="40140" windowHeight="30820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="464">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1531,6 +1531,30 @@
   </si>
   <si>
     <t>KB0039</t>
+  </si>
+  <si>
+    <t>KB0040</t>
+  </si>
+  <si>
+    <t>Rear projector not network accessible</t>
+  </si>
+  <si>
+    <t>Failure when trying to access the projector web page.</t>
+  </si>
+  <si>
+    <t>Attempt to access projector web page</t>
+  </si>
+  <si>
+    <t>Network cable fault</t>
+  </si>
+  <si>
+    <t>Terry to trace and repair cable</t>
+  </si>
+  <si>
+    <t>ZVVU-0001</t>
+  </si>
+  <si>
+    <t>#projector, #network</t>
   </si>
 </sst>
 </file>
@@ -1656,14 +1680,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O41" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O41" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="KB0039"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O42" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O41">
+    <sortCondition ref="A2:A41"/>
+  </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="13"/>
@@ -2002,7 +2023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -2058,7 +2079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -2081,7 +2102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -2122,7 +2143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -2166,7 +2187,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
@@ -2207,7 +2228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
@@ -2251,7 +2272,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
@@ -2292,7 +2313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -2333,7 +2354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -2374,7 +2395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>76</v>
       </c>
@@ -2412,7 +2433,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
@@ -2453,7 +2474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>94</v>
       </c>
@@ -2494,7 +2515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>99</v>
       </c>
@@ -2535,7 +2556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
@@ -2579,7 +2600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>117</v>
       </c>
@@ -2623,7 +2644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>126</v>
       </c>
@@ -2667,7 +2688,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>135</v>
       </c>
@@ -2708,7 +2729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>144</v>
       </c>
@@ -2749,7 +2770,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -2790,7 +2811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>162</v>
       </c>
@@ -2831,7 +2852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>170</v>
       </c>
@@ -2875,7 +2896,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>180</v>
       </c>
@@ -2919,7 +2940,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>190</v>
       </c>
@@ -2963,683 +2984,683 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="1">
+        <v>39</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="M24" s="1">
-        <v>23</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>433</v>
+        <v>207</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="J25" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="K25" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="M25" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O25" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>23</v>
+        <v>212</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>223</v>
+        <v>433</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>224</v>
+        <v>108</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="M26" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>227</v>
+        <v>430</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="M27" s="1">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="M28" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>254</v>
+        <v>434</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>427</v>
+        <v>235</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="M29" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="M30" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="M31" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>277</v>
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="M32" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>429</v>
+        <v>272</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>245</v>
+        <v>92</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="M33" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>276</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>277</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="M34" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>306</v>
+        <v>429</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="M35" s="1">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>310</v>
+        <v>431</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>313</v>
+        <v>441</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>314</v>
+        <v>442</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>315</v>
+        <v>443</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>316</v>
+        <v>444</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>47</v>
+        <v>445</v>
       </c>
       <c r="M36" s="1">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>311</v>
+        <v>74</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>422</v>
+        <v>297</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>317</v>
+        <v>22</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>423</v>
+        <v>298</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="M37" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="M38" s="1">
-        <v>39</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>430</v>
+        <v>310</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="M39" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>440</v>
+        <v>321</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>441</v>
+        <v>322</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>442</v>
+        <v>323</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>317</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>307</v>
+        <v>423</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>445</v>
+        <v>325</v>
       </c>
       <c r="M40" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+      <c r="O40" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>455</v>
       </c>
@@ -3681,6 +3702,47 @@
       </c>
       <c r="O41" s="1" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="M42" s="1">
+        <v>42</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA142B3B-B051-E946-A335-B94B65C85525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A654F2F-ED3C-7144-B57C-3DC9BE5D4E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="471">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1555,6 +1555,27 @@
   </si>
   <si>
     <t>#projector, #network</t>
+  </si>
+  <si>
+    <t>KB0041</t>
+  </si>
+  <si>
+    <t>Device appears offline to network</t>
+  </si>
+  <si>
+    <t>The AVL Assistant Dashboard reports a problem with the device</t>
+  </si>
+  <si>
+    <t>Monitor scans occurs when the device is powered off</t>
+  </si>
+  <si>
+    <t>Device is powered off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If system is intentionally powered off, no action required. If system is powered on (and has been for a few minutes) then check network cable, unplug, replug the cable. </t>
+  </si>
+  <si>
+    <t>May need to check both ends of cable</t>
   </si>
 </sst>
 </file>
@@ -1603,65 +1624,71 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1680,27 +1707,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O42" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O43" totalsRowShown="0" headerRowDxfId="16" dataDxfId="0">
+  <autoFilter ref="A1:O43" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O41">
     <sortCondition ref="A2:A41"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2023,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -2079,1670 +2106,1800 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1">
+      <c r="L2" s="4"/>
+      <c r="M2" s="4">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4">
         <v>1</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="M4" s="1">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4">
         <v>2</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="1">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4">
         <v>3</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="4">
         <v>4</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="M7" s="1">
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
         <v>4.5</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="M8" s="1">
+      <c r="L8" s="4"/>
+      <c r="M8" s="4">
         <v>5</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="1">
+      <c r="L9" s="4"/>
+      <c r="M9" s="4">
         <v>6</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="1">
+      <c r="L10" s="4"/>
+      <c r="M10" s="4">
         <v>9</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M11" s="1">
+      <c r="L11" s="4"/>
+      <c r="M11" s="4">
         <v>10</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M12" s="1">
+      <c r="L12" s="4"/>
+      <c r="M12" s="4">
         <v>11</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="M13" s="1">
+      <c r="L13" s="4"/>
+      <c r="M13" s="4">
         <v>12</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14" s="4">
         <v>13</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15" s="4">
         <v>14</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="1">
+      <c r="L16" s="4"/>
+      <c r="M16" s="4">
         <v>15</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="M17" s="1">
+      <c r="L17" s="4"/>
+      <c r="M17" s="4">
         <v>16</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N17" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="M18" s="1">
+      <c r="L18" s="4"/>
+      <c r="M18" s="4">
         <v>17</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N18" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M19" s="1">
+      <c r="L19" s="4"/>
+      <c r="M19" s="4">
         <v>18</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N19" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="M20" s="1">
+      <c r="L20" s="4"/>
+      <c r="M20" s="4">
         <v>19</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="M21" s="1">
+      <c r="L21" s="4"/>
+      <c r="M21" s="4">
         <v>20</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="O21" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="M22" s="1">
+      <c r="L22" s="4"/>
+      <c r="M22" s="4">
         <v>21</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="N22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="O22" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="M23" s="1">
+      <c r="L23" s="4"/>
+      <c r="M23" s="4">
         <v>22</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="O23" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="1">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4">
         <v>39</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="M25" s="1">
+      <c r="L25" s="4"/>
+      <c r="M25" s="4">
         <v>23</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="O25" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="M26" s="1">
+      <c r="L26" s="4"/>
+      <c r="M26" s="4">
         <v>24</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M27" s="1">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4">
         <v>40</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="M28" s="1">
+      <c r="L28" s="4"/>
+      <c r="M28" s="4">
         <v>25</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="O28" s="4" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="M29" s="1">
+      <c r="L29" s="4"/>
+      <c r="M29" s="4">
         <v>26</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="N29" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="O29" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="M30" s="1">
+      <c r="L30" s="4"/>
+      <c r="M30" s="4">
         <v>27</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="O30" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="M31" s="1">
+      <c r="L31" s="4"/>
+      <c r="M31" s="4">
         <v>28</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="O31" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="M32" s="1">
+      <c r="L32" s="4"/>
+      <c r="M32" s="4">
         <v>29</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="N32" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="O32" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="M33" s="1">
+      <c r="L33" s="4"/>
+      <c r="M33" s="4">
         <v>30</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="O33" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="J34" s="4"/>
+      <c r="K34" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="M34" s="1">
+      <c r="L34" s="4"/>
+      <c r="M34" s="4">
         <v>31</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="O34" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="M35" s="1">
+      <c r="L35" s="4"/>
+      <c r="M35" s="4">
         <v>32</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="O35" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="M36" s="1">
+      <c r="L36" s="4"/>
+      <c r="M36" s="4">
         <v>42</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="N36" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="M37" s="1">
+      <c r="L37" s="4"/>
+      <c r="M37" s="4">
         <v>33</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O37" s="1" t="s">
+      <c r="O37" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="M38" s="1">
+      <c r="L38" s="4"/>
+      <c r="M38" s="4">
         <v>34</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="N38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="4" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="L39" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39" s="4">
         <v>36</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="N39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="O39" s="4" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="M40" s="1">
+      <c r="L40" s="4"/>
+      <c r="M40" s="4">
         <v>38</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="N40" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="O40" s="4" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="M41" s="1">
+      <c r="L41" s="4"/>
+      <c r="M41" s="4">
         <v>41</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="N41" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="O41" s="4" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:15" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="M42" s="1">
+      <c r="L42" s="4"/>
+      <c r="M42" s="4">
         <v>42</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="N42" s="4" t="s">
         <v>31</v>
+      </c>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4">
+        <v>43</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A654F2F-ED3C-7144-B57C-3DC9BE5D4E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084B132C-49AB-1A4E-9FC8-C28BC62B3282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="476">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1577,12 +1577,27 @@
   <si>
     <t>May need to check both ends of cable</t>
   </si>
+  <si>
+    <t>KB0042</t>
+  </si>
+  <si>
+    <t>VS88 Video Matrix unresponsive to newtork</t>
+  </si>
+  <si>
+    <t>Does not repsond to network ping</t>
+  </si>
+  <si>
+    <t>Monitoring of network status if Kramer VS88DT video matrix, it doesn't respond to Ping</t>
+  </si>
+  <si>
+    <t>Physical device changes can confuse this device requiring a reboot.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1603,6 +1618,13 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1612,7 +1634,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1620,11 +1642,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF47D359"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF47D359"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF47D359"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF47D359"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF47D359"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF47D359"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF47D359"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF47D359"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1636,6 +1695,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1707,27 +1775,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O43" totalsRowShown="0" headerRowDxfId="16" dataDxfId="0">
-  <autoFilter ref="A1:O43" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O44" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O44" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O41">
     <sortCondition ref="A2:A41"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{99B6ADBC-8781-B846-821D-0367B521DD89}" name=" Category " dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B6DBC451-2B1C-F94A-A01B-8135E89CBAC8}" name=" Subcategory " dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{FB7DD802-E795-B047-BE37-D8BB7C6A5BAD}" name=" Title " dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{07201179-6B39-8949-844B-CEE11E6EDB49}" name=" Symptom " dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{0485B2F9-34C2-CA48-AB6F-0BC3BA51FBC0}" name=" TriggerConditions " dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{4183B9DE-D94A-BD4A-8F0E-B7A760717C5F}" name=" LikelyCause " dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{62C265AB-4FCB-1046-AF2C-3C97D014F136}" name=" RecoverySteps " dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{5A36F6EB-E991-8D4D-94E7-05C8CA75197F}" name=" AppliesToAssetType " dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{9AEAF97E-3F51-A043-A89E-F8F005226CB6}" name="AppliesToAssetTag" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{5C0A625C-1C65-5A4A-AF4C-D0F44F2906A2}" name=" Tags " dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{7FF7E833-E899-C24E-8BBE-767CE59AEB38}" name="SeeAlso" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{E3A9225A-7773-DA40-A1EE-0FBB1F1DFED4}" name=" SortOrder " dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{013C7458-C36D-8340-BDE2-1630AA3F099E}" name=" Active " dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{03B11681-0EC6-4C43-8C60-99EAC922882E}" name=" Notes " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2050,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -2781,7 +2849,9 @@
       <c r="K17" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="L17" s="4"/>
+      <c r="L17" s="6" t="s">
+        <v>471</v>
+      </c>
       <c r="M17" s="4">
         <v>16</v>
       </c>
@@ -3900,6 +3970,53 @@
       </c>
       <c r="O43" s="4" t="s">
         <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="M44" s="7">
+        <v>44</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084B132C-49AB-1A4E-9FC8-C28BC62B3282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7007EA63-CFA4-DE42-8677-BE15FBF440E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="484">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1591,6 +1591,30 @@
   </si>
   <si>
     <t>Physical device changes can confuse this device requiring a reboot.</t>
+  </si>
+  <si>
+    <t>KB0043</t>
+  </si>
+  <si>
+    <t>Keyboard stops working</t>
+  </si>
+  <si>
+    <t>When trying to operate Propresenter, the keyboard stops working</t>
+  </si>
+  <si>
+    <t>Seems to be a random event</t>
+  </si>
+  <si>
+    <t>Keyboard lost USB connection to the KVM unit.</t>
+  </si>
+  <si>
+    <t>unplug and replug the keyboard</t>
+  </si>
+  <si>
+    <t>CUMU-G002, 2603-1105</t>
+  </si>
+  <si>
+    <t>#propresenter, #keyboard</t>
   </si>
 </sst>
 </file>
@@ -1775,8 +1799,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O44" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O44" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O45" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O41">
     <sortCondition ref="A2:A41"/>
   </sortState>
@@ -2118,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -4018,6 +4042,51 @@
       <c r="O44" s="8" t="s">
         <v>475</v>
       </c>
+    </row>
+    <row r="45" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="M45" s="4">
+        <v>45</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7007EA63-CFA4-DE42-8677-BE15FBF440E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC828064-3D63-644C-AC6A-83D16148653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="484">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1799,10 +1799,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O45" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O41">
-    <sortCondition ref="A2:A41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O44" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O44" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O40">
+    <sortCondition ref="A2:A40"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F5D9425D-17E4-814F-893B-3266F2DAF7F0}" name=" IssueID " dataDxfId="14"/>
@@ -2142,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -3150,634 +3150,656 @@
     </row>
     <row r="24" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="25" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>207</v>
+        <v>433</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>208</v>
-      </c>
+      <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="4" t="s">
-        <v>210</v>
-      </c>
+      <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>211</v>
+        <v>430</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>430</v>
+        <v>218</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>225</v>
+      </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>22</v>
+        <v>228</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>23</v>
+        <v>229</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>223</v>
+        <v>434</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>434</v>
+        <v>244</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>74</v>
+        <v>249</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>245</v>
+        <v>427</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N30" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>427</v>
+        <v>298</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>298</v>
+        <v>92</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N33" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>282</v>
+        <v>429</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="J34" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>245</v>
+      </c>
       <c r="K34" s="4" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N34" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>285</v>
+        <v>431</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>288</v>
+        <v>442</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>289</v>
+        <v>443</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>290</v>
+        <v>445</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O35" s="4" t="s">
-        <v>291</v>
-      </c>
+      <c r="O35" s="4"/>
     </row>
     <row r="36" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>431</v>
+        <v>292</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>317</v>
+        <v>74</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>440</v>
+        <v>293</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>441</v>
+        <v>294</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>442</v>
+        <v>295</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>443</v>
+        <v>296</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>444</v>
+        <v>297</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>317</v>
+        <v>22</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>445</v>
+        <v>299</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O36" s="4"/>
+      <c r="O36" s="4" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="37" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>109</v>
+        <v>311</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>22</v>
+        <v>424</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>307</v>
+        <v>37</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="L38" s="4"/>
+        <v>318</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="M38" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>22</v>
@@ -3786,307 +3808,260 @@
         <v>311</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>316</v>
+        <v>422</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>37</v>
+        <v>423</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>47</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="L39" s="4"/>
       <c r="M39" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N39" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>319</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>320</v>
+        <v>455</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>311</v>
+        <v>109</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>321</v>
+        <v>447</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>322</v>
+        <v>448</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>323</v>
+        <v>449</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>324</v>
+        <v>450</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>317</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>325</v>
+        <v>453</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N40" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>317</v>
+        <v>28</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O41" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>462</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>463</v>
+        <v>283</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N42" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O42" s="4"/>
-    </row>
-    <row r="43" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4">
-        <v>43</v>
-      </c>
-      <c r="N43" s="4" t="s">
+      <c r="O42" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="M43" s="7">
+        <v>44</v>
+      </c>
+      <c r="N43" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O43" s="4" t="s">
-        <v>470</v>
+      <c r="O43" s="8" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="B44" s="7" t="s">
+      <c r="A44" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="M44" s="7">
-        <v>44</v>
-      </c>
-      <c r="N44" s="7" t="s">
+      <c r="C44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="M44" s="4">
+        <v>45</v>
+      </c>
+      <c r="N44" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O44" s="8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="M45" s="4">
-        <v>45</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O45" s="4"/>
+      <c r="O44" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC828064-3D63-644C-AC6A-83D16148653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8561E90-EC21-6940-9F25-D987D6FFA522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,9 +171,6 @@
     <t>Intermittent network connectivity issues between the control device, the network infrastructure, and the projector's internal web server, or the projector's network interface has frozen.</t>
   </si>
   <si>
-    <t>You need to be pretty much directly below each projection screen and point the remote at the projector. One remote will do all three but you will have to change the selector switch for each projector (not sure if the switch is labelled 1,2,3 or A,B,C.) The east screen is the "first" ( A or 1).</t>
-  </si>
-  <si>
     <t>#video, #projector, #network</t>
   </si>
   <si>
@@ -205,14 +202,6 @@
   </si>
   <si>
     <t>OBS software on CUMU-G001 displays a black screen or 'No Signal' message for the input from the Web Presenter, even though the Web Presenter itself shows an active video signal on its own display.</t>
-  </si>
-  <si>
-    <t>Occurs sporadically after system startup, or if the Web Presenter's USB connection to the computer (CUMU-G001) is
-         disturbed.</t>
-  </si>
-  <si>
-    <t>The USB driver for the Web Presenter on CUMU-G001 has become unresponsive, or the USB connection has momentarily dropped,
-         requiring a reset of the USB device to re-establish communication.</t>
   </si>
   <si>
     <t>Pull the plug and reinsert on the USB cable going into to the computer (CUMU-G001). The cable has a label "Web Camera"</t>
@@ -257,18 +246,6 @@
     <t>ProPresenter Lyric Overlay Not Appearing on ATEM</t>
   </si>
   <si>
-    <t>Upon activating the 'Key 1 Cut' in ATEM Software Control or pressing the 'Lyrics' button on the Stream Deck, the ProPresenter lyric
-         overlay fails to appear on the program output.</t>
-  </si>
-  <si>
-    <t>Observed when attempting to display lyric overlays after an ATEM software update, system reconfiguration, or if keyer
-         settings were manually adjusted.</t>
-  </si>
-  <si>
-    <t>Incorrect or altered 'Key 1' DSK (Downstream Keyer) settings within the ATEM software, specifically the 'Fill Source', 'Key
-         Source', or 'Key Type' parameters, preventing the overlay from rendering correctly.</t>
-  </si>
-  <si>
     <t>Return the key settings to correct values, running macro 1 is the easiest way to do so.</t>
   </si>
   <si>
@@ -290,17 +267,9 @@
     <t>Blackout Blind Detached from Side Track</t>
   </si>
   <si>
-    <t>A motorized blackout blind is visibly out of its side track, causing it to be stuck during movement or fail to fully seal against the
-         window frame.</t>
-  </si>
-  <si>
     <t>May occur during normal operation (raising or lowering the blind), or if the blind encounters an obstruction.</t>
   </si>
   <si>
-    <t>Misalignment or obstruction within the blind's track system, excessive tension on the fabric, or a mechanical issue with the
-         motor or winding mechanism causing it to dislodge.</t>
-  </si>
-  <si>
     <t>Running the blinds up and down a **little** bit at a time can sometimes get them back in their track. An assistant at the blind can reach in behind and help guide them in. If it is more than a few inches, a ladder may be required to reinsert the blind into the track.</t>
   </si>
   <si>
@@ -317,10 +286,6 @@
   </si>
   <si>
     <t>Adjusting faders or pressing playback buttons on the lighting console fails to alter the light levels or trigger programmed cues.</t>
-  </si>
-  <si>
-    <t>Observed upon starting the console, after loading a new show file, or if the console's operating mode was recently
-         changed.</t>
   </si>
   <si>
     <t xml:space="preserve"> The console is not in the correct operating mode (e.g., not in playback mode), or an 'override' or 'clear all' command has not been properly executed, leaving the console in a non-control state.</t>
@@ -345,32 +310,16 @@
     <t>Lighting Console Lacks Control While Lights Are On</t>
   </si>
   <si>
-    <t>Despite lighting fixtures being visibly illuminated, the lighting console fails to adjust their intensity, color, or other parameters
-         when faders are moved or cues are activated.</t>
-  </si>
-  <si>
     <t>Typically occurs after a system power cycle, or if a keypad preset has been activated that overrides console control.</t>
   </si>
   <si>
-    <t>A pre-programmed lighting scene or a DMX input from another source (like a keypad) is overriding the console's output, or the
-         console is not properly patched to the fixtures.</t>
-  </si>
-  <si>
     <t>KB0011</t>
   </si>
   <si>
     <t>ProPresenter Lighting Macros Not Triggering Console</t>
   </si>
   <si>
-    <t>Executing a lighting macro within ProPresenter (CUMU-G002) does not result in the expected lighting changes on the console
-         (ZLKU-C001).</t>
-  </si>
-  <si>
     <t>Observed when attempting to fire pre-programmed lighting cues from ProPresenter by clicking the associated macro.</t>
-  </si>
-  <si>
-    <t>The lighting automation software   (e.g., running on CUMU-G001) responsible for translating
-         ProPresenter commands to the lighting console is either not running or has crashed.</t>
   </si>
   <si>
     <t>1) Easiest way to fix this is to logoff CUMU-G001 and logon again.
@@ -395,15 +344,7 @@
     <t>ProPresenter Audio Not Reaching Audio Console (Dante)</t>
   </si>
   <si>
-    <t>Despite active audio meters within ProPresenter (CUMU-G002) during playback, no audio signal is received by the main audio console or
-         other Dante-enabled devices.</t>
-  </si>
-  <si>
     <t>Occurs upon system startup, after a reboot of CUMU-G002, or if Dante connectivity was recently interrupted.</t>
-  </si>
-  <si>
-    <t>The Dante Virtual Soundcard (DVS) application on CUMU-G002 is either not running or not correctly configured, preventing audio
-         routing to the Dante network.</t>
   </si>
   <si>
     <t>1) on CUMU-G002, start the program Dante Virtual Soundcard.
@@ -423,10 +364,6 @@
   </si>
   <si>
     <t>Reaper (Livestream) Not Receiving Audio Input (Dante)</t>
-  </si>
-  <si>
-    <t>Audio is present and audible in the Front of House (FoH) system, but the Reaper DAW on the livestream computer (CUMU-E001) shows no
-         incoming audio signal or active meters.</t>
   </si>
   <si>
     <t>Typically observed after the livestream computer (CUMU-E001) startup, or if Dante connectivity has been interrupted.</t>
@@ -490,9 +427,6 @@
   </si>
   <si>
     <t>System hung</t>
-  </si>
-  <si>
-    <t>power cycle the ZVKU-A001 device using the power button on the rear.</t>
   </si>
   <si>
     <t>#ZVKU-A001</t>
@@ -1043,10 +977,6 @@
   </si>
   <si>
     <t>Waking CUMU-G002 from sleep or booting up when the KVM switch is slow to initialize.</t>
-  </si>
-  <si>
-    <t>KVM switch latency causes the OS to identify the secondary projection output as the primary
-     display, placing the login dialog on a screen not visible to the operator.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Remote login via ScreenConnect or Screen Sharing (from CUMU-G001 go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
@@ -1615,6 +1545,60 @@
   </si>
   <si>
     <t>#propresenter, #keyboard</t>
+  </si>
+  <si>
+    <t>Executing a lighting macro within ProPresenter (CUMU-G002) does not result in the expected lighting changes on the console (ZLKU-C001).</t>
+  </si>
+  <si>
+    <t>The lighting automation software   (e.g., running on CUMU-G001) responsible for translating ProPresenter commands to the lighting console is either not running or has crashed.</t>
+  </si>
+  <si>
+    <t>The Dante Virtual Soundcard (DVS) application on CUMU-G002 is either not running or not correctly configured, preventing audio routing to the Dante network.</t>
+  </si>
+  <si>
+    <t>Despite active audio meters within ProPresenter (CUMU-G002) during playback, no audio signal is received by the main audio console or other Dante-enabled devices.</t>
+  </si>
+  <si>
+    <t>You need to be pretty much directly below each projection screen and point the remote at the projector.  One remote will do all three but you will have to change the selector switch for each projector (not sure if the switch is labelled 1,2,3 or A,B,C.) The east screen is the "first" ( A or 1).</t>
+  </si>
+  <si>
+    <t>Occurs sporadically after system startup, or if the Web Presenter's USB connection to the computer (CUMU-G001) is disturbed.</t>
+  </si>
+  <si>
+    <t>The USB driver for the Web Presenter on CUMU-G001 has become unresponsive, or the USB connection has momentarily dropped, requiring a reset of the USB device to re-establish communication.</t>
+  </si>
+  <si>
+    <t>Upon activating the 'Key 1 Cut' in ATEM Software Control or pressing the 'Lyrics' button on the Stream Deck, the ProPresenter lyric overlay fails to appear on the program output.</t>
+  </si>
+  <si>
+    <t>Observed when attempting to display lyric overlays after an ATEM software update, system reconfiguration, or if keyer settings were manually adjusted.</t>
+  </si>
+  <si>
+    <t>Incorrect or altered 'Key 1' DSK (Downstream Keyer) settings within the ATEM software, specifically the 'Fill Source', 'Key Source', or 'Key Type' parameters, preventing the overlay from rendering correctly.</t>
+  </si>
+  <si>
+    <t>Misalignment or obstruction within the blind's track system, excessive tension on the fabric, or a mechanical issue with the motor or winding mechanism causing it to dislodge.</t>
+  </si>
+  <si>
+    <t>A motorized blackout blind is visibly out of its side track, causing it to be stuck during movement or fail to fully seal against the window frame.</t>
+  </si>
+  <si>
+    <t>Observed upon starting the console, after loading a new show file, or if the console's operating mode was recently changed.</t>
+  </si>
+  <si>
+    <t>A pre-programmed lighting scene or a DMX input from another source (like a keypad) is overriding the console's output, or the console is not properly patched to the fixtures.</t>
+  </si>
+  <si>
+    <t>Despite lighting fixtures being visibly illuminated, the lighting console fails to adjust their intensity, color, or other parameters when faders are moved or cues are activated.</t>
+  </si>
+  <si>
+    <t>Audio is present and audible in the Front of House (FoH) system, but the Reaper DAW on the livestream computer (CUMU-E001) shows no  incoming audio signal or active meters.</t>
+  </si>
+  <si>
+    <t>Power cycle the ZVKU-A001 device using the power button on the rear.</t>
+  </si>
+  <si>
+    <t>KVM switch latency causes the OS to identify the secondary projection output as the primary display, placing the login dialog on a screen not visible to the operator.</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2230,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>26</v>
@@ -2292,19 +2276,19 @@
         <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4">
@@ -2340,16 +2324,16 @@
         <v>44</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>45</v>
+        <v>470</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4">
@@ -2362,7 +2346,7 @@
     </row>
     <row r="6" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>22</v>
@@ -2371,22 +2355,22 @@
         <v>33</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>37</v>
@@ -2395,7 +2379,7 @@
         <v>38</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="M6" s="4">
         <v>4</v>
@@ -2407,37 +2391,37 @@
     </row>
     <row r="7" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="I7" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="K7" s="4" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4">
@@ -2450,7 +2434,7 @@
     </row>
     <row r="8" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>22</v>
@@ -2459,28 +2443,28 @@
         <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="K8" s="4" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4">
@@ -2493,7 +2477,7 @@
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>22</v>
@@ -2502,28 +2486,28 @@
         <v>33</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4">
@@ -2536,35 +2520,35 @@
     </row>
     <row r="10" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4">
@@ -2577,37 +2561,37 @@
     </row>
     <row r="11" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>89</v>
+        <v>478</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4">
@@ -2620,37 +2604,37 @@
     </row>
     <row r="12" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>96</v>
+        <v>480</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>98</v>
+        <v>479</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4">
@@ -2663,37 +2647,37 @@
     </row>
     <row r="13" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>101</v>
+        <v>466</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>103</v>
+        <v>467</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4">
@@ -2706,40 +2690,40 @@
     </row>
     <row r="14" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>111</v>
+        <v>469</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>113</v>
+        <v>468</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="M14" s="4">
         <v>13</v>
@@ -2751,40 +2735,40 @@
     </row>
     <row r="15" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="K15" s="4" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M15" s="4">
         <v>14</v>
@@ -2796,7 +2780,7 @@
     </row>
     <row r="16" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>22</v>
@@ -2805,28 +2789,28 @@
         <v>33</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4">
@@ -2836,45 +2820,45 @@
         <v>31</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>141</v>
+        <v>482</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="M17" s="4">
         <v>16</v>
@@ -2886,37 +2870,37 @@
     </row>
     <row r="18" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4">
@@ -2929,37 +2913,37 @@
     </row>
     <row r="19" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4">
@@ -2972,37 +2956,37 @@
     </row>
     <row r="20" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4">
@@ -3015,37 +2999,37 @@
     </row>
     <row r="21" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4">
@@ -3055,42 +3039,42 @@
         <v>31</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4">
@@ -3100,42 +3084,42 @@
         <v>31</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4">
@@ -3145,42 +3129,42 @@
         <v>31</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4">
@@ -3190,40 +3174,40 @@
         <v>31</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4">
@@ -3236,7 +3220,7 @@
     </row>
     <row r="26" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -3261,7 +3245,7 @@
     </row>
     <row r="27" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>22</v>
@@ -3270,28 +3254,28 @@
         <v>23</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4">
@@ -3301,87 +3285,87 @@
         <v>31</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4">
         <v>26</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4">
@@ -3391,42 +3375,42 @@
         <v>31</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4">
@@ -3436,42 +3420,42 @@
         <v>31</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4">
@@ -3481,42 +3465,42 @@
         <v>31</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4">
@@ -3526,40 +3510,40 @@
         <v>31</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4">
@@ -3569,42 +3553,42 @@
         <v>31</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4">
@@ -3614,42 +3598,42 @@
         <v>31</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4">
@@ -3662,37 +3646,37 @@
     </row>
     <row r="36" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4">
@@ -3702,42 +3686,42 @@
         <v>31</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>305</v>
+        <v>483</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4">
@@ -3747,45 +3731,45 @@
         <v>31</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M38" s="4">
         <v>36</v>
@@ -3794,42 +3778,42 @@
         <v>31</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4">
@@ -3839,42 +3823,42 @@
         <v>31</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4">
@@ -3884,12 +3868,12 @@
         <v>31</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>22</v>
@@ -3898,28 +3882,28 @@
         <v>23</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4">
@@ -3932,33 +3916,33 @@
     </row>
     <row r="42" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4">
@@ -3968,45 +3952,45 @@
         <v>31</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>141</v>
+        <v>482</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="M43" s="7">
         <v>44</v>
@@ -4015,45 +3999,45 @@
         <v>31</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="M44" s="4">
         <v>45</v>
@@ -4078,477 +4062,477 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8561E90-EC21-6940-9F25-D987D6FFA522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8377738D-F493-8546-940C-EB7D361F7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="493">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1599,6 +1599,33 @@
   </si>
   <si>
     <t>KVM switch latency causes the OS to identify the secondary projection output as the primary display, placing the login dialog on a screen not visible to the operator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The video desk wants to see the single wide video content on the ATEM. Or the HDMI output needs to be routed directly to the projectors. </t>
+  </si>
+  <si>
+    <t>HDMI output from CUMU-G002 is non-operable.</t>
+  </si>
+  <si>
+    <t>The HDMI output from the USB dock, 2410-1607. Plugging it into causes disruption of the displays on computer (CUMU-G002); primary and secondary displays are swapped which may be a challenge to deal with if the operator is not prepared.</t>
+  </si>
+  <si>
+    <t>See the recovery steps for KB0036.</t>
+  </si>
+  <si>
+    <t>Computer, Control, Video</t>
+  </si>
+  <si>
+    <t>CUMU-G002, 2410-1607, 2601-2800, 2311-2701</t>
+  </si>
+  <si>
+    <t>KB0044</t>
+  </si>
+  <si>
+    <t>Unable to see Single Wide (SW) HDMI output on ATEM or projectors.</t>
+  </si>
+  <si>
+    <t>Propresenter should be closed/quit when physically connecting or disconnecting the HDMI output.</t>
   </si>
 </sst>
 </file>
@@ -1783,8 +1810,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O44" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O44" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O45" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O40">
     <sortCondition ref="A2:A40"/>
   </sortState>
@@ -2126,13 +2153,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
-    <col min="4" max="15" width="25.83203125" style="1" customWidth="1"/>
+    <col min="4" max="8" width="25.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
@@ -3955,7 +3989,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>453</v>
       </c>
@@ -4002,7 +4036,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>458</v>
       </c>
@@ -4046,6 +4080,53 @@
         <v>31</v>
       </c>
       <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="M45" s="4">
+        <v>45</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>492</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8377738D-F493-8546-940C-EB7D361F7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EE29B4-E359-D546-A563-23ED020AFFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="494">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1469,9 +1469,6 @@
     <t>Rear projector not network accessible</t>
   </si>
   <si>
-    <t>Failure when trying to access the projector web page.</t>
-  </si>
-  <si>
     <t>Attempt to access projector web page</t>
   </si>
   <si>
@@ -1626,6 +1623,12 @@
   </si>
   <si>
     <t>Propresenter should be closed/quit when physically connecting or disconnecting the HDMI output.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failure when trying to access the projector web page. Projector menu says there is no IP address. </t>
+  </si>
+  <si>
+    <t>MAC Address on record is correct with projector menu.</t>
   </si>
 </sst>
 </file>
@@ -2358,7 +2361,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>28</v>
@@ -2440,10 +2443,10 @@
         <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>56</v>
@@ -2523,13 +2526,13 @@
         <v>66</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>67</v>
@@ -2566,13 +2569,13 @@
         <v>73</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>75</v>
@@ -2610,7 +2613,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>81</v>
@@ -2650,13 +2653,13 @@
         <v>86</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>419</v>
@@ -2693,13 +2696,13 @@
         <v>89</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>91</v>
@@ -2736,13 +2739,13 @@
         <v>97</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>99</v>
@@ -2781,7 +2784,7 @@
         <v>104</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>105</v>
@@ -2880,7 +2883,7 @@
         <v>124</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>68</v>
@@ -2892,7 +2895,7 @@
         <v>126</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M17" s="4">
         <v>16</v>
@@ -3743,7 +3746,7 @@
         <v>287</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>288</v>
@@ -3905,7 +3908,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="5" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>438</v>
       </c>
@@ -3919,25 +3922,25 @@
         <v>439</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J41" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="K41" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4">
@@ -3946,11 +3949,13 @@
       <c r="N41" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O41" s="4"/>
+      <c r="O41" s="4" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="42" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>260</v>
@@ -3959,19 +3964,19 @@
         <v>260</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -3986,12 +3991,12 @@
         <v>31</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>22</v>
@@ -4000,19 +4005,19 @@
         <v>68</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="F43" s="7" t="s">
         <v>455</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>456</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>124</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>68</v>
@@ -4033,12 +4038,12 @@
         <v>31</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>22</v>
@@ -4047,28 +4052,28 @@
         <v>96</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>299</v>
       </c>
       <c r="J44" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="K44" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>465</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>437</v>
@@ -4083,7 +4088,7 @@
     </row>
     <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>22</v>
@@ -4092,25 +4097,25 @@
         <v>96</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E45" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="J45" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>420</v>
@@ -4125,7 +4130,7 @@
         <v>31</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EE29B4-E359-D546-A563-23ED020AFFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5AC2AC-0AE7-B549-B84B-71C4A97FF96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="501">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1629,6 +1629,31 @@
   </si>
   <si>
     <t>MAC Address on record is correct with projector menu.</t>
+  </si>
+  <si>
+    <t>KB0045</t>
+  </si>
+  <si>
+    <t>Video Stream Deck Unresponsive</t>
+  </si>
+  <si>
+    <t>The normal stream deck button functions are not available or don't work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possibilities include:
+1) Companion is not running on CUMU-G001. 
+2) USB cable has become unplugged. </t>
+  </si>
+  <si>
+    <t>2603-1301,  CUMU-G001, 2601-2800</t>
+  </si>
+  <si>
+    <t>#video, #mixer, #atem</t>
+  </si>
+  <si>
+    <t>1) check connections
+2) Reboot CUMU-G001
+3) As a fallback, use the buttons that are on the front face of the video mixer in the rack. You can view the multiview display on the video hub 2507-0700 monitor .</t>
   </si>
 </sst>
 </file>
@@ -1813,8 +1838,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O45" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O46" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O46" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O40">
     <sortCondition ref="A2:A40"/>
   </sortState>
@@ -2156,7 +2181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -4133,6 +4158,49 @@
         <v>491</v>
       </c>
     </row>
+    <row r="46" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="M46" s="4">
+        <v>46</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O46" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5AC2AC-0AE7-B549-B84B-71C4A97FF96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEAF3B-3DAD-DC4A-B91A-5BA7BEDF4C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="526">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1654,6 +1654,85 @@
     <t>1) check connections
 2) Reboot CUMU-G001
 3) As a fallback, use the buttons that are on the front face of the video mixer in the rack. You can view the multiview display on the video hub 2507-0700 monitor .</t>
+  </si>
+  <si>
+    <t>KB0046</t>
+  </si>
+  <si>
+    <t>Lights don't respond even though console is powered on and operating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firing a Cue, or manually setting a look doesn't result in a lighting change. </t>
+  </si>
+  <si>
+    <t>There is an overriding control that is preventing the lights from repsonding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) If exepcting on of the cues to first, make sure that the executor master fader for the sequence is at 100% ( usually the first fader). 
+2) The "Blind" or  "Prvw" buttons might be active. They are in the centre of the console. They are lit when active. Press them to turn them off. </t>
+  </si>
+  <si>
+    <t>Lighting, Control</t>
+  </si>
+  <si>
+    <t>2507-2500</t>
+  </si>
+  <si>
+    <t>#lighting, #control</t>
+  </si>
+  <si>
+    <t>KB0047</t>
+  </si>
+  <si>
+    <t>Montior does not respond</t>
+  </si>
+  <si>
+    <t>Unsure of what can cause this. It happened once after a major power failure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause not determined. </t>
+  </si>
+  <si>
+    <t>Computer, Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) try selecting inputs hdmi1 and hdmi2. 
+2) Verify that the computer is on (indicator light is on)
+3) try logging in from another computer either using MacOS screen sharing or the remote access solution. If you can than that indicates the problem is with the video subsystem and not the computer itself.
+4) open the rack (2602-1800) side panels to locate the decimator (ZVIU-C001), there is a red hdmi cable (2310-1004) plugged into that device.  Unplug it and replug. </t>
+  </si>
+  <si>
+    <t>CUMU-G002, 2311-2701, ZVIU-C001, 2310-1004</t>
+  </si>
+  <si>
+    <t>Despite the monitor (2311-2701) being powered on and hdmi 1 or 2 are selected, the display remains black.</t>
+  </si>
+  <si>
+    <t>KB0048</t>
+  </si>
+  <si>
+    <t>Audio system does not power up despite the touch panel appearing to behave normally.</t>
+  </si>
+  <si>
+    <t>Pressing the Power button on the touch screeen intiates the normal power up animations, but the system does not actually power on. The gear beside the surface does not power up, nor does the surface itself, nor the amplifiers in the main rack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This has been observed after a major power outage that outlasted the UPS reserve. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss of system power left the control system in a confused state. </t>
+  </si>
+  <si>
+    <t>From one of the media arts Mac computers, login to the website http://192.168.200.50/.  You will get a warning about the website not being private. This is acceptable. Click Show details, and then "visit this website" - message text could be slightly different depening on which browser you are using. Navigate to "utilities" on the left hand side, and then select "Reboot" beside "Core Reboot". It will take a few minutes to complete. Then try the touch screen again.</t>
+  </si>
+  <si>
+    <t>2408-2704, 2407-3001</t>
+  </si>
+  <si>
+    <t>#audio, #power</t>
+  </si>
+  <si>
+    <t>#video, #monitor</t>
   </si>
 </sst>
 </file>
@@ -1838,8 +1917,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O46" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O46" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O49" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O49" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O40">
     <sortCondition ref="A2:A40"/>
   </sortState>
@@ -2181,7 +2260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -4201,6 +4280,133 @@
       </c>
       <c r="O46" s="4"/>
     </row>
+    <row r="47" spans="1:15" ht="187" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4">
+        <v>47</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4">
+        <v>47</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4">
+        <v>48</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O49" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEAF3B-3DAD-DC4A-B91A-5BA7BEDF4C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB160F4-9690-8041-8F03-9B0414B3CCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="526">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -972,16 +972,7 @@
     <t>Presenter Login Dialog Missing on Local Monitor</t>
   </si>
   <si>
-    <t>Local monitor shows only the desktop background/wallpaper with no login fields, icons, or
-     interactive elements.</t>
-  </si>
-  <si>
     <t>Waking CUMU-G002 from sleep or booting up when the KVM switch is slow to initialize.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Remote login via ScreenConnect or Screen Sharing (from CUMU-G001 go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
-2. Route the "PPHD" source to the ATEM Program/Preview monitor to see and interact with the dialog. OR 
-3. (Hardware  Fix) Unplug cable 2308-0918 from the rear of CUMU-G002 to force the OS to use the local monitor. </t>
   </si>
   <si>
     <t>CUMU-G002</t>
@@ -1668,10 +1659,6 @@
     <t>There is an overriding control that is preventing the lights from repsonding.</t>
   </si>
   <si>
-    <t xml:space="preserve">1) If exepcting on of the cues to first, make sure that the executor master fader for the sequence is at 100% ( usually the first fader). 
-2) The "Blind" or  "Prvw" buttons might be active. They are in the centre of the console. They are lit when active. Press them to turn them off. </t>
-  </si>
-  <si>
     <t>Lighting, Control</t>
   </si>
   <si>
@@ -1733,6 +1720,20 @@
   </si>
   <si>
     <t>#video, #monitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) If exepcting on of the cues to first, make sure that the executor master fader for the sequence is at 100% ( usually the first fader). 
+2) The "Blind" or  "Prvw" buttons might be active. If they are in the centre of the console. They are lit when active. Press them to turn them off. </t>
+  </si>
+  <si>
+    <t>Local monitor shows only the desktop background/wallpaper with no login fields, icons, or interactive elements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try each of these in order:
+1. On the stream deck, select "Main Menu", then "Video Menu", then "VIdeo Hub".  There are now two buttons at the bottom "PP Operator 1" and "PP Operator 2". Press each in turn until you see the login prompt.
+2. Remote login via ScreenConnect or Screen Sharing (from CUMU-G001 go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
+3. Route the "PPHD" source to the ATEM Program/Preview monitor to see and interact with the dialog. OR 
+4. (Hardware  Fix) Unplug cable 2308-0918 from the rear of CUMU-G002 to force the OS to use the local monitor. </t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2372,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>26</v>
@@ -2417,10 +2418,10 @@
         <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>68</v>
@@ -2429,7 +2430,7 @@
         <v>37</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4">
@@ -2465,13 +2466,13 @@
         <v>44</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>45</v>
@@ -2520,7 +2521,7 @@
         <v>38</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M6" s="4">
         <v>4</v>
@@ -2547,22 +2548,22 @@
         <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4">
@@ -2605,7 +2606,7 @@
         <v>64</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4">
@@ -2630,13 +2631,13 @@
         <v>66</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>67</v>
@@ -2673,19 +2674,19 @@
         <v>73</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
@@ -2717,7 +2718,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>81</v>
@@ -2757,16 +2758,16 @@
         <v>86</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>68</v>
@@ -2800,13 +2801,13 @@
         <v>89</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>91</v>
@@ -2820,7 +2821,9 @@
       <c r="K13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>499</v>
+      </c>
       <c r="M13" s="4">
         <v>12</v>
       </c>
@@ -2843,13 +2846,13 @@
         <v>97</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>99</v>
@@ -2888,7 +2891,7 @@
         <v>104</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>105</v>
@@ -2987,7 +2990,7 @@
         <v>124</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>68</v>
@@ -2999,7 +3002,7 @@
         <v>126</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M17" s="4">
         <v>16</v>
@@ -3341,7 +3344,7 @@
         <v>199</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>95</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="26" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -3452,7 +3455,7 @@
         <v>216</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>217</v>
@@ -3548,7 +3551,7 @@
         <v>95</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>238</v>
@@ -3720,7 +3723,7 @@
         <v>272</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>68</v>
@@ -3744,37 +3747,37 @@
     </row>
     <row r="35" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="I35" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4">
@@ -3830,7 +3833,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" s="5" customFormat="1" ht="263" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>284</v>
       </c>
@@ -3844,25 +3847,25 @@
         <v>285</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>288</v>
+        <v>525</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4">
@@ -3872,42 +3875,42 @@
         <v>31</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>298</v>
-      </c>
       <c r="I38" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>46</v>
@@ -3919,42 +3922,42 @@
         <v>31</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="H39" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="K39" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4">
@@ -3964,12 +3967,12 @@
         <v>31</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>22</v>
@@ -3978,28 +3981,28 @@
         <v>96</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="I40" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="K40" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4">
@@ -4009,12 +4012,12 @@
         <v>31</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="5" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>22</v>
@@ -4023,28 +4026,28 @@
         <v>23</v>
       </c>
       <c r="D41" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4">
@@ -4054,12 +4057,12 @@
         <v>31</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>260</v>
@@ -4068,19 +4071,19 @@
         <v>260</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -4095,12 +4098,12 @@
         <v>31</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>22</v>
@@ -4109,19 +4112,19 @@
         <v>68</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>453</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>455</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>124</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>68</v>
@@ -4142,12 +4145,12 @@
         <v>31</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>22</v>
@@ -4156,31 +4159,31 @@
         <v>96</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="I44" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="K44" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>464</v>
-      </c>
       <c r="L44" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M44" s="4">
         <v>45</v>
@@ -4192,7 +4195,7 @@
     </row>
     <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>22</v>
@@ -4201,28 +4204,28 @@
         <v>96</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E45" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="J45" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="K45" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>284</v>
@@ -4234,12 +4237,12 @@
         <v>31</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="136" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>22</v>
@@ -4248,29 +4251,29 @@
         <v>241</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="K46" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="I46" s="4" t="s">
+      <c r="L46" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="M46" s="4">
         <v>46</v>
@@ -4282,7 +4285,7 @@
     </row>
     <row r="47" spans="1:15" ht="187" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>71</v>
@@ -4291,28 +4294,30 @@
         <v>78</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="K47" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="L47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="M47" s="4">
         <v>47</v>
       </c>
@@ -4323,7 +4328,7 @@
     </row>
     <row r="48" spans="1:15" ht="306" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>22</v>
@@ -4332,28 +4337,28 @@
         <v>96</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="G48" s="4" t="s">
+      <c r="J48" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>515</v>
-      </c>
       <c r="K48" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4">
@@ -4364,9 +4369,9 @@
       </c>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>95</v>
@@ -4375,28 +4380,28 @@
         <v>68</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="H49" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>522</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>68</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4">
@@ -4422,477 +4427,477 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB160F4-9690-8041-8F03-9B0414B3CCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC9CC24-1279-A342-BF61-A21FF5F76DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,9 +1730,9 @@
   </si>
   <si>
     <t xml:space="preserve">Try each of these in order:
-1. On the stream deck, select "Main Menu", then "Video Menu", then "VIdeo Hub".  There are now two buttons at the bottom "PP Operator 1" and "PP Operator 2". Press each in turn until you see the login prompt.
-2. Remote login via ScreenConnect or Screen Sharing (from CUMU-G001 go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
-3. Route the "PPHD" source to the ATEM Program/Preview monitor to see and interact with the dialog. OR 
+1. On the stream deck, select "Main Menu", then "Video Menu", then "VIdeo Hub".  There are now two buttons at the bottom "PP Operator 1" and "PP Operator 2". Press each in turn until you see the login prompt. OR
+2. Remote login via ScreenConnect or Screen Sharing (from CUMU-G001) go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
+3. Route the "PPHD" source to the ATEM Program/Preview monitor to see and interact with the dialog,  go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
 4. (Hardware  Fix) Unplug cable 2308-0918 from the rear of CUMU-G002 to force the OS to use the local monitor. </t>
   </si>
 </sst>

--- a/knowledgebase.xlsx
+++ b/knowledgebase.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC9CC24-1279-A342-BF61-A21FF5F76DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341CE5BD-3C0E-F449-81F9-D9345DDCFC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="540">
   <si>
     <t xml:space="preserve"> IssueID </t>
   </si>
@@ -1735,12 +1736,75 @@
 3. Route the "PPHD" source to the ATEM Program/Preview monitor to see and interact with the dialog,  go to System Settings &gt; Displays &gt; Arrange, and drag the white menu bar to the local monitor. OR 
 4. (Hardware  Fix) Unplug cable 2308-0918 from the rear of CUMU-G002 to force the OS to use the local monitor. </t>
   </si>
+  <si>
+    <t xml:space="preserve">Reaper periodically goes silent for a few seconds. </t>
+  </si>
+  <si>
+    <t>During livestream operation, all audio inputs go silent, for perhaps 3 seconds, and then it returns to normal operation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With Dante Controller running, wait for the event to recur. Dante Controller's event log shows an error "Resolution Failed" for CUMU-E001. </t>
+  </si>
+  <si>
+    <t>Root cause unknown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If still in rehearsal (ie not actively broadcasting):
+1) Reboot CUMU-E001.
+If broadcasting: 
+1) Set the house dlive console's video matrix to mirror the FOH audio, but at elevated levels.This could be done on the physical surface (2407-3001) or via dlive director (2607-2321).
+2) Using the Q-SYS touchpad (2408-2704) or the app on CUMU-E001, switch video source to 'Matrix'. 
+3) Reboot CUMU-E001 and re-establish the Reaper session.
+4) Using the Q-SYS touchpad (2408-2704) or the app on CUMU-E001, switch video source to 'DAW'.
+If sitation continues to occur, consider switching the video source to Matrix. You can actively mix the inputs using the matrix mix on dlive director.  </t>
+  </si>
+  <si>
+    <t>Audio, Computer</t>
+  </si>
+  <si>
+    <t>CUMU-E001, 2607-2302, 2607-2306</t>
+  </si>
+  <si>
+    <t>#audio, #dante</t>
+  </si>
+  <si>
+    <t>This has only happened once.</t>
+  </si>
+  <si>
+    <t>KB0049</t>
+  </si>
+  <si>
+    <t>Root cause unknown. The Dante 'Resolution Failed' error for CUMU-E001 in the event log points to a Dante device-discovery/name-resolution dropout rather than a Reaper fault.</t>
+  </si>
+  <si>
+    <t>This has only happened once; during rehearsal on 2026-08-23.</t>
+  </si>
+  <si>
+    <t>With Dante Controller running, wait for the event to recur. Dante Controller's event log shows an error "Resolution Failed" for CUMU-E001. 
+If the event recurs, capture diagnostics before rebooting (the reboot clears the event state):
+In Dante Controller, navigate to the 'Events' tab and use the 'Save' button at the bottom to capture the event diagnostics for later review.
+While in the 'Events' tab, check whether the errors are logged only against CUMU-E001 or against multiple devices. Errors on CUMU-E001 alone suggest a fault local to that node; errors across several devices suggest a wider Dante network problem (switch, clock/PTP, or cabling).
+In the device list, note whether CUMU-E001 briefly disappears at the moment of the dropout, or stays present but drops its subscriptions. Disappearing points to a discovery/name-resolution fault; staying present with lost subscriptions points to a subscription/flow fault.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: Video' matrix and 'Video Send' selector are named for the video broadcast they feed, but both carry audio. Normal operation for broadcasting runs with 'Video Send' set to 'DAW'
+If still in rehearsal (ie not actively broadcasting):
+1) Capture diagnostics per TriggerConditions (save the Events log and note single-node vs. system-wide).
+2) Reboot CUMU-E001.
+If broadcasting:
+1) Set the house dlive console's 'Video' matrix (the backup audio mix for the broadcast) to mirror the FOH audio, but at elevated levels. This can be done on the physical surface (2407-3001) or via dlive director (2607-2321).
+2) Using the Q-SYS touchpad (2408-2704) or the app on CUMU-E001, set 'Video Send' to 'Matrix'.
+3) Capture diagnostics per TriggerConditions (save the Events log and note single-node vs. system-wide, before rebooting).
+4) Reboot CUMU-E001 and re-establish the Reaper session.
+5) Using the Q-SYS touchpad (2408-2704) or the app on CUMU-E001, set 'Video Send' back to 'DAW'."
+If situation continues to occur, consider switching the video source to Matrix. You can actively mix the inputs using the matrix mix on dlive director.  </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1768,16 +1832,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1822,11 +1906,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1846,6 +1967,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1918,8 +2057,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O49" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O49" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}" name="Table1" displayName="Table1" ref="A1:O50" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O50" xr:uid="{8DA13CB4-8680-0D4C-A016-6564C2E20834}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O40">
     <sortCondition ref="A2:A40"/>
   </sortState>
@@ -2261,7 +2400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -4412,6 +4551,53 @@
       </c>
       <c r="O49" s="4"/>
     </row>
+    <row r="50" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M50" s="4">
+        <v>50</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4903,4 +5089,138 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D34FA1E-DACB-4A40-A2D8-391D868E6BDF}">
+  <dimension ref="A2:B16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="2" max="2" width="137.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="85" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="204" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="255" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>534</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>